--- a/Rev. 0/Excel/PET_SNES_BOM_v0_0.xlsx
+++ b/Rev. 0/Excel/PET_SNES_BOM_v0_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Projekte\_Eigene\PET_CBM_Projects\PET_SNES_Gamepad_Adapter\Rev. 0\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{EF9E4973-3442-4A21-897B-2A306F8BA5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C14F8E0-B3A3-40D5-B950-1C788E6D9AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3192" yWindow="1284" windowWidth="27036" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Stückliste!$A$1:$F$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Stückliste!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -168,6 +168,21 @@
   </si>
   <si>
     <t>CUI Inc., RCA jack, vertical, red. Mouser: 490-RCJ-022, Digikey:  CP-1407-ND. Alternative part: Keystone 577</t>
+  </si>
+  <si>
+    <t>CUI Inc., RCA jack, vertical, white. Mouser: 490-RCJ-023, Digikey:  CP-1408-ND. Alternative part: Keystone 584</t>
+  </si>
+  <si>
+    <t>1/4W, 1% or better</t>
+  </si>
+  <si>
+    <t>Resistor network 4 pin, 5 resistors</t>
+  </si>
+  <si>
+    <t>ceramic capacitor, pitch: 2.5mm</t>
+  </si>
+  <si>
+    <t>Vertical SNES Gamepad Connector from Ali Express</t>
   </si>
   <si>
     <r>
@@ -190,36 +205,27 @@
         <rFont val="Futura Lt BT"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">5.0mm/pitch 2.0mm 105°C, l=11mm, e.G. Reichelt RD1C106M05011180 </t>
+      <t>5.0mm/pitch 2.0mm 105°C, l=11mm, e.G. Reichelt RD1C106M05011180 . Lay flat on board.</t>
     </r>
-  </si>
-  <si>
-    <t>CUI Inc., RCA jack, vertical, white. Mouser: 490-RCJ-023, Digikey:  CP-1408-ND. Alternative part: Keystone 584</t>
-  </si>
-  <si>
-    <t>1/4W, 1% or better</t>
-  </si>
-  <si>
-    <t>Resistor network 4 pin, 5 resistors</t>
-  </si>
-  <si>
-    <t>ceramic capacitor, pitch: 2.5mm</t>
-  </si>
-  <si>
-    <t>Vertical SNES Gamepad Connector from Ali Express</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Futura Lt BT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -688,50 +694,50 @@
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -739,10 +745,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -754,25 +760,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1284,24 +1293,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
     </row>
     <row r="3" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1330,25 +1339,28 @@
       <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3">
+        <f>A4+1</f>
+        <v>2</v>
+      </c>
       <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -1357,16 +1369,19 @@
       <c r="E5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>52</v>
+      <c r="F5" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3">
+        <f t="shared" ref="A6:A16" si="0">A5+1</f>
+        <v>3</v>
+      </c>
       <c r="B6" s="3">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>24</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1375,16 +1390,19 @@
       <c r="E6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+      <c r="F6" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -1393,16 +1411,19 @@
       <c r="E7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>48</v>
+      <c r="F7" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -1411,16 +1432,19 @@
       <c r="E8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1429,16 +1453,19 @@
       <c r="E9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="10" t="s">
@@ -1447,16 +1474,19 @@
       <c r="E10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -1465,16 +1495,19 @@
       <c r="E11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="10" t="s">
@@ -1483,16 +1516,19 @@
       <c r="E12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>49</v>
+      <c r="F12" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
       <c r="B13" s="3">
         <v>1</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>38</v>
       </c>
       <c r="D13" s="10" t="s">
@@ -1501,16 +1537,19 @@
       <c r="E13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="14" t="s">
-        <v>53</v>
+      <c r="F13" s="12" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="10" t="s">
@@ -1519,16 +1558,19 @@
       <c r="E14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>50</v>
+      <c r="F14" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
       <c r="B15" s="3">
         <v>1</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="10" t="s">
@@ -1537,16 +1579,19 @@
       <c r="E15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>50</v>
+      <c r="F15" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
       <c r="B16" s="3">
         <v>1</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -1555,8 +1600,8 @@
       <c r="E16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>51</v>
+      <c r="F16" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2092,6 +2137,9 @@
 Drafted by Sven Petersen&amp;C&amp;"Futura Lt BT,Light"Page &amp;P of &amp;N&amp;R&amp;"Futura Lt BT,Light"&amp;D &amp;T
 Doc.No.: 221-5-01-00.0</oddFooter>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A4" calculatedColumn="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
   </tableParts>
